--- a/data/APP.xlsx
+++ b/data/APP.xlsx
@@ -35714,10 +35714,10 @@
         <v>46276.5625</v>
       </c>
       <c r="B1360" t="n">
-        <v>3741959</v>
+        <v>3751600</v>
       </c>
       <c r="C1360" t="n">
-        <v>325.599914550781</v>
+        <v>325.600006103516</v>
       </c>
       <c r="D1360" t="n">
         <v>311.679992675781</v>
@@ -35732,6 +35732,32 @@
         <v>323.959991455078</v>
       </c>
       <c r="H1360" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" s="1" t="n">
+        <v>46279.5625</v>
+      </c>
+      <c r="B1361" t="n">
+        <v>4793359</v>
+      </c>
+      <c r="C1361" t="n">
+        <v>338.339996337891</v>
+      </c>
+      <c r="D1361" t="n">
+        <v>320.399993896484</v>
+      </c>
+      <c r="E1361" t="n">
+        <v>324.070007324219</v>
+      </c>
+      <c r="F1361" t="n">
+        <v>334.239990234375</v>
+      </c>
+      <c r="G1361" t="n">
+        <v>334.239990234375</v>
+      </c>
+      <c r="H1361" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/APP.xlsx
+++ b/data/APP.xlsx
@@ -35740,7 +35740,7 @@
         <v>46279.5625</v>
       </c>
       <c r="B1361" t="n">
-        <v>4793359</v>
+        <v>5056600</v>
       </c>
       <c r="C1361" t="n">
         <v>338.339996337891</v>
@@ -35749,7 +35749,7 @@
         <v>320.399993896484</v>
       </c>
       <c r="E1361" t="n">
-        <v>324.070007324219</v>
+        <v>324.040008544922</v>
       </c>
       <c r="F1361" t="n">
         <v>334.239990234375</v>
@@ -35758,6 +35758,32 @@
         <v>334.239990234375</v>
       </c>
       <c r="H1361" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" s="1" t="n">
+        <v>46280.5625</v>
+      </c>
+      <c r="B1362" t="n">
+        <v>6496272</v>
+      </c>
+      <c r="C1362" t="n">
+        <v>334.459991455078</v>
+      </c>
+      <c r="D1362" t="n">
+        <v>323.802490234375</v>
+      </c>
+      <c r="E1362" t="n">
+        <v>328.325012207031</v>
+      </c>
+      <c r="F1362" t="n">
+        <v>331.459991455078</v>
+      </c>
+      <c r="G1362" t="n">
+        <v>331.459991455078</v>
+      </c>
+      <c r="H1362" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/APP.xlsx
+++ b/data/APP.xlsx
@@ -35766,13 +35766,13 @@
         <v>46280.5625</v>
       </c>
       <c r="B1362" t="n">
-        <v>6496272</v>
+        <v>6604900</v>
       </c>
       <c r="C1362" t="n">
         <v>334.459991455078</v>
       </c>
       <c r="D1362" t="n">
-        <v>323.802490234375</v>
+        <v>323.803009033203</v>
       </c>
       <c r="E1362" t="n">
         <v>328.325012207031</v>
@@ -35784,6 +35784,32 @@
         <v>331.459991455078</v>
       </c>
       <c r="H1362" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" s="1" t="n">
+        <v>46281.5625</v>
+      </c>
+      <c r="B1363" t="n">
+        <v>3519066</v>
+      </c>
+      <c r="C1363" t="n">
+        <v>336.390014648438</v>
+      </c>
+      <c r="D1363" t="n">
+        <v>322.010009765625</v>
+      </c>
+      <c r="E1363" t="n">
+        <v>333.579986572266</v>
+      </c>
+      <c r="F1363" t="n">
+        <v>326.559997558594</v>
+      </c>
+      <c r="G1363" t="n">
+        <v>326.559997558594</v>
+      </c>
+      <c r="H1363" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/APP.xlsx
+++ b/data/APP.xlsx
@@ -35792,10 +35792,10 @@
         <v>46281.5625</v>
       </c>
       <c r="B1363" t="n">
-        <v>3519066</v>
+        <v>3522600</v>
       </c>
       <c r="C1363" t="n">
-        <v>336.390014648438</v>
+        <v>336.440002441406</v>
       </c>
       <c r="D1363" t="n">
         <v>322.010009765625</v>
@@ -35810,6 +35810,32 @@
         <v>326.559997558594</v>
       </c>
       <c r="H1363" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" s="1" t="n">
+        <v>46282.5625</v>
+      </c>
+      <c r="B1364" t="n">
+        <v>4390043</v>
+      </c>
+      <c r="C1364" t="n">
+        <v>333.430908203125</v>
+      </c>
+      <c r="D1364" t="n">
+        <v>314.839996337891</v>
+      </c>
+      <c r="E1364" t="n">
+        <v>331.859985351562</v>
+      </c>
+      <c r="F1364" t="n">
+        <v>321.600006103516</v>
+      </c>
+      <c r="G1364" t="n">
+        <v>321.600006103516</v>
+      </c>
+      <c r="H1364" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/APP.xlsx
+++ b/data/APP.xlsx
@@ -35818,13 +35818,13 @@
         <v>46282.5625</v>
       </c>
       <c r="B1364" t="n">
-        <v>4390043</v>
+        <v>4537400</v>
       </c>
       <c r="C1364" t="n">
-        <v>333.430908203125</v>
+        <v>333.430999755859</v>
       </c>
       <c r="D1364" t="n">
-        <v>314.839996337891</v>
+        <v>314.820007324219</v>
       </c>
       <c r="E1364" t="n">
         <v>331.859985351562</v>
@@ -35836,6 +35836,32 @@
         <v>321.600006103516</v>
       </c>
       <c r="H1364" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" s="1" t="n">
+        <v>46283.5625</v>
+      </c>
+      <c r="B1365" t="n">
+        <v>10877792</v>
+      </c>
+      <c r="C1365" t="n">
+        <v>328.149993896484</v>
+      </c>
+      <c r="D1365" t="n">
+        <v>307.760009765625</v>
+      </c>
+      <c r="E1365" t="n">
+        <v>323.390014648438</v>
+      </c>
+      <c r="F1365" t="n">
+        <v>308.059997558594</v>
+      </c>
+      <c r="G1365" t="n">
+        <v>308.059997558594</v>
+      </c>
+      <c r="H1365" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/APP.xlsx
+++ b/data/APP.xlsx
@@ -35844,7 +35844,7 @@
         <v>46283.5625</v>
       </c>
       <c r="B1365" t="n">
-        <v>10877792</v>
+        <v>10936300</v>
       </c>
       <c r="C1365" t="n">
         <v>328.149993896484</v>
@@ -35862,6 +35862,32 @@
         <v>308.059997558594</v>
       </c>
       <c r="H1365" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" s="1" t="n">
+        <v>46286.5625</v>
+      </c>
+      <c r="B1366" t="n">
+        <v>5966341</v>
+      </c>
+      <c r="C1366" t="n">
+        <v>336.940002441406</v>
+      </c>
+      <c r="D1366" t="n">
+        <v>306.799987792969</v>
+      </c>
+      <c r="E1366" t="n">
+        <v>308.690002441406</v>
+      </c>
+      <c r="F1366" t="n">
+        <v>330.170013427734</v>
+      </c>
+      <c r="G1366" t="n">
+        <v>330.170013427734</v>
+      </c>
+      <c r="H1366" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/APP.xlsx
+++ b/data/APP.xlsx
@@ -35844,7 +35844,7 @@
         <v>46283.5625</v>
       </c>
       <c r="B1365" t="n">
-        <v>10936300</v>
+        <v>10960500</v>
       </c>
       <c r="C1365" t="n">
         <v>328.149993896484</v>
@@ -35870,7 +35870,7 @@
         <v>46286.5625</v>
       </c>
       <c r="B1366" t="n">
-        <v>5966341</v>
+        <v>5991100</v>
       </c>
       <c r="C1366" t="n">
         <v>336.940002441406</v>
@@ -35879,7 +35879,7 @@
         <v>306.799987792969</v>
       </c>
       <c r="E1366" t="n">
-        <v>308.690002441406</v>
+        <v>309.690002441406</v>
       </c>
       <c r="F1366" t="n">
         <v>330.170013427734</v>
@@ -35888,6 +35888,32 @@
         <v>330.170013427734</v>
       </c>
       <c r="H1366" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" s="1" t="n">
+        <v>46287.5625</v>
+      </c>
+      <c r="B1367" t="n">
+        <v>3368623</v>
+      </c>
+      <c r="C1367" t="n">
+        <v>333.570007324219</v>
+      </c>
+      <c r="D1367" t="n">
+        <v>323.679992675781</v>
+      </c>
+      <c r="E1367" t="n">
+        <v>333</v>
+      </c>
+      <c r="F1367" t="n">
+        <v>328.730010986328</v>
+      </c>
+      <c r="G1367" t="n">
+        <v>328.730010986328</v>
+      </c>
+      <c r="H1367" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/APP.xlsx
+++ b/data/APP.xlsx
@@ -31795,7 +31795,7 @@
         <v>46288.5625</v>
       </c>
       <c r="B1367" t="n">
-        <v>6775407</v>
+        <v>6803700</v>
       </c>
       <c r="C1367" t="n">
         <v>316.5</v>
@@ -31810,6 +31810,29 @@
         <v>315.25</v>
       </c>
       <c r="G1367" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" s="1" t="n">
+        <v>46289.5625</v>
+      </c>
+      <c r="B1368" t="n">
+        <v>3944546</v>
+      </c>
+      <c r="C1368" t="n">
+        <v>320.445007324219</v>
+      </c>
+      <c r="D1368" t="n">
+        <v>308.239990234375</v>
+      </c>
+      <c r="E1368" t="n">
+        <v>315.5</v>
+      </c>
+      <c r="F1368" t="n">
+        <v>312.470001220703</v>
+      </c>
+      <c r="G1368" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/APP.xlsx
+++ b/data/APP.xlsx
@@ -35974,10 +35974,10 @@
         <v>46290.5625</v>
       </c>
       <c r="B1370" t="n">
-        <v>3007024</v>
+        <v>3020100</v>
       </c>
       <c r="C1370" t="n">
-        <v>316</v>
+        <v>316.010009765625</v>
       </c>
       <c r="D1370" t="n">
         <v>308.329986572266</v>
@@ -35992,6 +35992,32 @@
         <v>310.75</v>
       </c>
       <c r="H1370" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="A1371" s="1" t="n">
+        <v>46293.5625</v>
+      </c>
+      <c r="B1371" t="n">
+        <v>4120929</v>
+      </c>
+      <c r="C1371" t="n">
+        <v>322.738006591797</v>
+      </c>
+      <c r="D1371" t="n">
+        <v>306.880096435547</v>
+      </c>
+      <c r="E1371" t="n">
+        <v>322.738006591797</v>
+      </c>
+      <c r="F1371" t="n">
+        <v>308.239990234375</v>
+      </c>
+      <c r="G1371" t="n">
+        <v>308.239990234375</v>
+      </c>
+      <c r="H1371" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/APP.xlsx
+++ b/data/APP.xlsx
@@ -36000,16 +36000,16 @@
         <v>46293.5625</v>
       </c>
       <c r="B1371" t="n">
-        <v>4120929</v>
+        <v>4171800</v>
       </c>
       <c r="C1371" t="n">
         <v>322.738006591797</v>
       </c>
       <c r="D1371" t="n">
-        <v>306.880096435547</v>
+        <v>306.880004882812</v>
       </c>
       <c r="E1371" t="n">
-        <v>322.738006591797</v>
+        <v>322.045013427734</v>
       </c>
       <c r="F1371" t="n">
         <v>308.239990234375</v>
@@ -36018,6 +36018,32 @@
         <v>308.239990234375</v>
       </c>
       <c r="H1371" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" s="1" t="n">
+        <v>46294.5625</v>
+      </c>
+      <c r="B1372" t="n">
+        <v>3677717</v>
+      </c>
+      <c r="C1372" t="n">
+        <v>313.380004882812</v>
+      </c>
+      <c r="D1372" t="n">
+        <v>304.839996337891</v>
+      </c>
+      <c r="E1372" t="n">
+        <v>309</v>
+      </c>
+      <c r="F1372" t="n">
+        <v>305.660003662109</v>
+      </c>
+      <c r="G1372" t="n">
+        <v>305.660003662109</v>
+      </c>
+      <c r="H1372" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/APP.xlsx
+++ b/data/APP.xlsx
@@ -36026,7 +36026,7 @@
         <v>46294.5625</v>
       </c>
       <c r="B1372" t="n">
-        <v>3677717</v>
+        <v>3729400</v>
       </c>
       <c r="C1372" t="n">
         <v>313.380004882812</v>
@@ -36044,6 +36044,32 @@
         <v>305.660003662109</v>
       </c>
       <c r="H1372" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" s="1" t="n">
+        <v>46295.5625</v>
+      </c>
+      <c r="B1373" t="n">
+        <v>6352688</v>
+      </c>
+      <c r="C1373" t="n">
+        <v>303.169891357422</v>
+      </c>
+      <c r="D1373" t="n">
+        <v>290.399993896484</v>
+      </c>
+      <c r="E1373" t="n">
+        <v>299.880004882812</v>
+      </c>
+      <c r="F1373" t="n">
+        <v>290.429992675781</v>
+      </c>
+      <c r="G1373" t="n">
+        <v>290.429992675781</v>
+      </c>
+      <c r="H1373" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/APP.xlsx
+++ b/data/APP.xlsx
@@ -36052,16 +36052,16 @@
         <v>46295.5625</v>
       </c>
       <c r="B1373" t="n">
-        <v>6352688</v>
+        <v>6734300</v>
       </c>
       <c r="C1373" t="n">
-        <v>303.169891357422</v>
+        <v>303.170013427734</v>
       </c>
       <c r="D1373" t="n">
-        <v>290.399993896484</v>
+        <v>290.359985351562</v>
       </c>
       <c r="E1373" t="n">
-        <v>299.880004882812</v>
+        <v>299.5</v>
       </c>
       <c r="F1373" t="n">
         <v>290.429992675781</v>
@@ -36070,6 +36070,32 @@
         <v>290.429992675781</v>
       </c>
       <c r="H1373" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="A1374" s="1" t="n">
+        <v>46296.5625</v>
+      </c>
+      <c r="B1374" t="n">
+        <v>7947302</v>
+      </c>
+      <c r="C1374" t="n">
+        <v>291.345001220703</v>
+      </c>
+      <c r="D1374" t="n">
+        <v>275.130004882812</v>
+      </c>
+      <c r="E1374" t="n">
+        <v>291</v>
+      </c>
+      <c r="F1374" t="n">
+        <v>281.309997558594</v>
+      </c>
+      <c r="G1374" t="n">
+        <v>281.309997558594</v>
+      </c>
+      <c r="H1374" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/APP.xlsx
+++ b/data/APP.xlsx
@@ -36078,10 +36078,10 @@
         <v>46296.5625</v>
       </c>
       <c r="B1374" t="n">
-        <v>7947302</v>
+        <v>8021700</v>
       </c>
       <c r="C1374" t="n">
-        <v>291.345001220703</v>
+        <v>291.545013427734</v>
       </c>
       <c r="D1374" t="n">
         <v>275.130004882812</v>
@@ -36096,6 +36096,32 @@
         <v>281.309997558594</v>
       </c>
       <c r="H1374" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="A1375" s="1" t="n">
+        <v>46297.5625</v>
+      </c>
+      <c r="B1375" t="n">
+        <v>8862212</v>
+      </c>
+      <c r="C1375" t="n">
+        <v>279.940002441406</v>
+      </c>
+      <c r="D1375" t="n">
+        <v>266.839996337891</v>
+      </c>
+      <c r="E1375" t="n">
+        <v>269.450012207031</v>
+      </c>
+      <c r="F1375" t="n">
+        <v>268.220001220703</v>
+      </c>
+      <c r="G1375" t="n">
+        <v>268.220001220703</v>
+      </c>
+      <c r="H1375" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/APP.xlsx
+++ b/data/APP.xlsx
@@ -36104,7 +36104,7 @@
         <v>46297.5625</v>
       </c>
       <c r="B1375" t="n">
-        <v>8862212</v>
+        <v>8880600</v>
       </c>
       <c r="C1375" t="n">
         <v>279.940002441406</v>
@@ -36113,7 +36113,7 @@
         <v>266.839996337891</v>
       </c>
       <c r="E1375" t="n">
-        <v>269.450012207031</v>
+        <v>270.174987792969</v>
       </c>
       <c r="F1375" t="n">
         <v>268.220001220703</v>
@@ -36122,6 +36122,32 @@
         <v>268.220001220703</v>
       </c>
       <c r="H1375" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="A1376" s="1" t="n">
+        <v>46300.5625</v>
+      </c>
+      <c r="B1376" t="n">
+        <v>6817633</v>
+      </c>
+      <c r="C1376" t="n">
+        <v>287.179992675781</v>
+      </c>
+      <c r="D1376" t="n">
+        <v>270</v>
+      </c>
+      <c r="E1376" t="n">
+        <v>270.510009765625</v>
+      </c>
+      <c r="F1376" t="n">
+        <v>281.970001220703</v>
+      </c>
+      <c r="G1376" t="n">
+        <v>281.970001220703</v>
+      </c>
+      <c r="H1376" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/APP.xlsx
+++ b/data/APP.xlsx
@@ -36104,7 +36104,7 @@
         <v>46297.5625</v>
       </c>
       <c r="B1375" t="n">
-        <v>8880600</v>
+        <v>8969000</v>
       </c>
       <c r="C1375" t="n">
         <v>279.940002441406</v>
@@ -36130,16 +36130,16 @@
         <v>46300.5625</v>
       </c>
       <c r="B1376" t="n">
-        <v>6817633</v>
+        <v>6894700</v>
       </c>
       <c r="C1376" t="n">
-        <v>287.179992675781</v>
+        <v>287.200012207031</v>
       </c>
       <c r="D1376" t="n">
         <v>270</v>
       </c>
       <c r="E1376" t="n">
-        <v>270.510009765625</v>
+        <v>270.614990234375</v>
       </c>
       <c r="F1376" t="n">
         <v>281.970001220703</v>
@@ -36148,6 +36148,32 @@
         <v>281.970001220703</v>
       </c>
       <c r="H1376" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1377">
+      <c r="A1377" s="1" t="n">
+        <v>46301.5625</v>
+      </c>
+      <c r="B1377" t="n">
+        <v>4268206</v>
+      </c>
+      <c r="C1377" t="n">
+        <v>283.759887695312</v>
+      </c>
+      <c r="D1377" t="n">
+        <v>276.660003662109</v>
+      </c>
+      <c r="E1377" t="n">
+        <v>282.730010986328</v>
+      </c>
+      <c r="F1377" t="n">
+        <v>278.779998779297</v>
+      </c>
+      <c r="G1377" t="n">
+        <v>278.779998779297</v>
+      </c>
+      <c r="H1377" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/APP.xlsx
+++ b/data/APP.xlsx
@@ -36156,10 +36156,10 @@
         <v>46301.5625</v>
       </c>
       <c r="B1377" t="n">
-        <v>4268206</v>
+        <v>4363000</v>
       </c>
       <c r="C1377" t="n">
-        <v>283.759887695312</v>
+        <v>283.760009765625</v>
       </c>
       <c r="D1377" t="n">
         <v>276.660003662109</v>
@@ -36174,6 +36174,32 @@
         <v>278.779998779297</v>
       </c>
       <c r="H1377" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="A1378" s="1" t="n">
+        <v>46302.5625</v>
+      </c>
+      <c r="B1378" t="n">
+        <v>3518674</v>
+      </c>
+      <c r="C1378" t="n">
+        <v>281.339996337891</v>
+      </c>
+      <c r="D1378" t="n">
+        <v>269.410003662109</v>
+      </c>
+      <c r="E1378" t="n">
+        <v>274.223999023438</v>
+      </c>
+      <c r="F1378" t="n">
+        <v>281.290008544922</v>
+      </c>
+      <c r="G1378" t="n">
+        <v>281.290008544922</v>
+      </c>
+      <c r="H1378" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/APP.xlsx
+++ b/data/APP.xlsx
@@ -36182,7 +36182,7 @@
         <v>46302.5625</v>
       </c>
       <c r="B1378" t="n">
-        <v>3518674</v>
+        <v>3528000</v>
       </c>
       <c r="C1378" t="n">
         <v>281.339996337891</v>
@@ -36191,7 +36191,7 @@
         <v>269.410003662109</v>
       </c>
       <c r="E1378" t="n">
-        <v>274.223999023438</v>
+        <v>274.845001220703</v>
       </c>
       <c r="F1378" t="n">
         <v>281.290008544922</v>
@@ -36200,6 +36200,32 @@
         <v>281.290008544922</v>
       </c>
       <c r="H1378" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" s="1" t="n">
+        <v>46303.5625</v>
+      </c>
+      <c r="B1379" t="n">
+        <v>5946587</v>
+      </c>
+      <c r="C1379" t="n">
+        <v>280.119995117188</v>
+      </c>
+      <c r="D1379" t="n">
+        <v>271.100006103516</v>
+      </c>
+      <c r="E1379" t="n">
+        <v>277.5</v>
+      </c>
+      <c r="F1379" t="n">
+        <v>280.119995117188</v>
+      </c>
+      <c r="G1379" t="n">
+        <v>280.119995117188</v>
+      </c>
+      <c r="H1379" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/APP.xlsx
+++ b/data/APP.xlsx
@@ -36208,7 +36208,7 @@
         <v>46303.5625</v>
       </c>
       <c r="B1379" t="n">
-        <v>5946587</v>
+        <v>6124800</v>
       </c>
       <c r="C1379" t="n">
         <v>280.119995117188</v>
@@ -36217,7 +36217,7 @@
         <v>271.100006103516</v>
       </c>
       <c r="E1379" t="n">
-        <v>277.5</v>
+        <v>276.079986572266</v>
       </c>
       <c r="F1379" t="n">
         <v>280.119995117188</v>
@@ -36226,6 +36226,32 @@
         <v>280.119995117188</v>
       </c>
       <c r="H1379" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="A1380" s="1" t="n">
+        <v>46304.5625</v>
+      </c>
+      <c r="B1380" t="n">
+        <v>3282034</v>
+      </c>
+      <c r="C1380" t="n">
+        <v>282.299987792969</v>
+      </c>
+      <c r="D1380" t="n">
+        <v>275.350006103516</v>
+      </c>
+      <c r="E1380" t="n">
+        <v>281.529998779297</v>
+      </c>
+      <c r="F1380" t="n">
+        <v>277.040008544922</v>
+      </c>
+      <c r="G1380" t="n">
+        <v>277.040008544922</v>
+      </c>
+      <c r="H1380" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/APP.xlsx
+++ b/data/APP.xlsx
@@ -36234,10 +36234,10 @@
         <v>46304.5625</v>
       </c>
       <c r="B1380" t="n">
-        <v>3282034</v>
+        <v>3310800</v>
       </c>
       <c r="C1380" t="n">
-        <v>282.299987792969</v>
+        <v>282.489990234375</v>
       </c>
       <c r="D1380" t="n">
         <v>275.350006103516</v>

--- a/data/APP.xlsx
+++ b/data/APP.xlsx
@@ -36286,7 +36286,7 @@
         <v>46308.5625</v>
       </c>
       <c r="B1382" t="n">
-        <v>3730430</v>
+        <v>3830900</v>
       </c>
       <c r="C1382" t="n">
         <v>276.950012207031</v>
@@ -36295,7 +36295,7 @@
         <v>267</v>
       </c>
       <c r="E1382" t="n">
-        <v>268.100006103516</v>
+        <v>268.274993896484</v>
       </c>
       <c r="F1382" t="n">
         <v>272.279998779297</v>
@@ -36304,6 +36304,32 @@
         <v>272.279998779297</v>
       </c>
       <c r="H1382" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="A1383" s="1" t="n">
+        <v>46309.5625</v>
+      </c>
+      <c r="B1383" t="n">
+        <v>4302214</v>
+      </c>
+      <c r="C1383" t="n">
+        <v>273</v>
+      </c>
+      <c r="D1383" t="n">
+        <v>261</v>
+      </c>
+      <c r="E1383" t="n">
+        <v>270.130004882812</v>
+      </c>
+      <c r="F1383" t="n">
+        <v>262.190002441406</v>
+      </c>
+      <c r="G1383" t="n">
+        <v>262.190002441406</v>
+      </c>
+      <c r="H1383" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/APP.xlsx
+++ b/data/APP.xlsx
@@ -36312,7 +36312,7 @@
         <v>46309.5625</v>
       </c>
       <c r="B1383" t="n">
-        <v>4302214</v>
+        <v>4348300</v>
       </c>
       <c r="C1383" t="n">
         <v>273</v>
@@ -36321,7 +36321,7 @@
         <v>261</v>
       </c>
       <c r="E1383" t="n">
-        <v>270.130004882812</v>
+        <v>270.200012207031</v>
       </c>
       <c r="F1383" t="n">
         <v>262.190002441406</v>
@@ -36330,6 +36330,32 @@
         <v>262.190002441406</v>
       </c>
       <c r="H1383" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="A1384" s="1" t="n">
+        <v>46310.5625</v>
+      </c>
+      <c r="B1384" t="n">
+        <v>4366175</v>
+      </c>
+      <c r="C1384" t="n">
+        <v>280.249908447266</v>
+      </c>
+      <c r="D1384" t="n">
+        <v>260.989990234375</v>
+      </c>
+      <c r="E1384" t="n">
+        <v>261.720001220703</v>
+      </c>
+      <c r="F1384" t="n">
+        <v>279.290008544922</v>
+      </c>
+      <c r="G1384" t="n">
+        <v>279.290008544922</v>
+      </c>
+      <c r="H1384" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/APP.xlsx
+++ b/data/APP.xlsx
@@ -36338,13 +36338,13 @@
         <v>46310.5625</v>
       </c>
       <c r="B1384" t="n">
-        <v>4366175</v>
+        <v>4371200</v>
       </c>
       <c r="C1384" t="n">
-        <v>280.249908447266</v>
+        <v>280.25</v>
       </c>
       <c r="D1384" t="n">
-        <v>260.989990234375</v>
+        <v>260.589996337891</v>
       </c>
       <c r="E1384" t="n">
         <v>261.720001220703</v>
@@ -36356,6 +36356,32 @@
         <v>279.290008544922</v>
       </c>
       <c r="H1384" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1385">
+      <c r="A1385" s="1" t="n">
+        <v>46311.5625</v>
+      </c>
+      <c r="B1385" t="n">
+        <v>3497793</v>
+      </c>
+      <c r="C1385" t="n">
+        <v>280.809997558594</v>
+      </c>
+      <c r="D1385" t="n">
+        <v>264.311096191406</v>
+      </c>
+      <c r="E1385" t="n">
+        <v>279.875</v>
+      </c>
+      <c r="F1385" t="n">
+        <v>266.130004882812</v>
+      </c>
+      <c r="G1385" t="n">
+        <v>266.130004882812</v>
+      </c>
+      <c r="H1385" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/APP.xlsx
+++ b/data/APP.xlsx
@@ -40551,7 +40551,7 @@
         <v>46314.5625</v>
       </c>
       <c r="C1386" t="n">
-        <v>269.369995117188</v>
+        <v>269.450012207031</v>
       </c>
       <c r="D1386" t="n">
         <v>270.399993896484</v>
@@ -40566,9 +40566,38 @@
         <v>269.119995117188</v>
       </c>
       <c r="H1386" t="n">
-        <v>2906322</v>
+        <v>2908000</v>
       </c>
       <c r="I1386" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="A1387" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1387" s="1" t="n">
+        <v>46315.5625</v>
+      </c>
+      <c r="C1387" t="n">
+        <v>269.450012207031</v>
+      </c>
+      <c r="D1387" t="n">
+        <v>277.440002441406</v>
+      </c>
+      <c r="E1387" t="n">
+        <v>267.278594970703</v>
+      </c>
+      <c r="F1387" t="n">
+        <v>272.459991455078</v>
+      </c>
+      <c r="G1387" t="n">
+        <v>272.459991455078</v>
+      </c>
+      <c r="H1387" t="n">
+        <v>2444947</v>
+      </c>
+      <c r="I1387" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/APP.xlsx
+++ b/data/APP.xlsx
@@ -40580,13 +40580,13 @@
         <v>46315.5625</v>
       </c>
       <c r="C1387" t="n">
-        <v>269.450012207031</v>
+        <v>269.329986572266</v>
       </c>
       <c r="D1387" t="n">
         <v>277.440002441406</v>
       </c>
       <c r="E1387" t="n">
-        <v>267.278594970703</v>
+        <v>267.278991699219</v>
       </c>
       <c r="F1387" t="n">
         <v>272.459991455078</v>
@@ -40595,9 +40595,38 @@
         <v>272.459991455078</v>
       </c>
       <c r="H1387" t="n">
-        <v>2444947</v>
+        <v>2448300</v>
       </c>
       <c r="I1387" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="A1388" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1388" s="1" t="n">
+        <v>46316.5625</v>
+      </c>
+      <c r="C1388" t="n">
+        <v>271.380004882812</v>
+      </c>
+      <c r="D1388" t="n">
+        <v>272.649993896484</v>
+      </c>
+      <c r="E1388" t="n">
+        <v>264.079986572266</v>
+      </c>
+      <c r="F1388" t="n">
+        <v>267.899993896484</v>
+      </c>
+      <c r="G1388" t="n">
+        <v>267.899993896484</v>
+      </c>
+      <c r="H1388" t="n">
+        <v>2710685</v>
+      </c>
+      <c r="I1388" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/APP.xlsx
+++ b/data/APP.xlsx
@@ -40624,9 +40624,38 @@
         <v>267.899993896484</v>
       </c>
       <c r="H1388" t="n">
-        <v>2710685</v>
+        <v>2722300</v>
       </c>
       <c r="I1388" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="A1389" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1389" s="1" t="n">
+        <v>46317.5625</v>
+      </c>
+      <c r="C1389" t="n">
+        <v>265.399993896484</v>
+      </c>
+      <c r="D1389" t="n">
+        <v>270.600006103516</v>
+      </c>
+      <c r="E1389" t="n">
+        <v>260.973999023438</v>
+      </c>
+      <c r="F1389" t="n">
+        <v>264.279998779297</v>
+      </c>
+      <c r="G1389" t="n">
+        <v>264.279998779297</v>
+      </c>
+      <c r="H1389" t="n">
+        <v>2851813</v>
+      </c>
+      <c r="I1389" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/APP.xlsx
+++ b/data/APP.xlsx
@@ -40638,13 +40638,13 @@
         <v>46317.5625</v>
       </c>
       <c r="C1389" t="n">
-        <v>265.399993896484</v>
+        <v>265.25</v>
       </c>
       <c r="D1389" t="n">
         <v>270.600006103516</v>
       </c>
       <c r="E1389" t="n">
-        <v>260.973999023438</v>
+        <v>260.950012207031</v>
       </c>
       <c r="F1389" t="n">
         <v>264.279998779297</v>
@@ -40653,9 +40653,38 @@
         <v>264.279998779297</v>
       </c>
       <c r="H1389" t="n">
-        <v>2851813</v>
+        <v>2853200</v>
       </c>
       <c r="I1389" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="A1390" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1390" s="1" t="n">
+        <v>46318.5625</v>
+      </c>
+      <c r="C1390" t="n">
+        <v>263.035003662109</v>
+      </c>
+      <c r="D1390" t="n">
+        <v>264</v>
+      </c>
+      <c r="E1390" t="n">
+        <v>258.320098876953</v>
+      </c>
+      <c r="F1390" t="n">
+        <v>260.25</v>
+      </c>
+      <c r="G1390" t="n">
+        <v>260.25</v>
+      </c>
+      <c r="H1390" t="n">
+        <v>2344713</v>
+      </c>
+      <c r="I1390" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/APP.xlsx
+++ b/data/APP.xlsx
@@ -40673,7 +40673,7 @@
         <v>264</v>
       </c>
       <c r="E1390" t="n">
-        <v>258.320098876953</v>
+        <v>258.320007324219</v>
       </c>
       <c r="F1390" t="n">
         <v>260.25</v>
@@ -40682,9 +40682,38 @@
         <v>260.25</v>
       </c>
       <c r="H1390" t="n">
-        <v>2344713</v>
+        <v>2348400</v>
       </c>
       <c r="I1390" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1391" s="1" t="n">
+        <v>46321.5625</v>
+      </c>
+      <c r="C1391" t="n">
+        <v>261.100006103516</v>
+      </c>
+      <c r="D1391" t="n">
+        <v>262.931213378906</v>
+      </c>
+      <c r="E1391" t="n">
+        <v>255.460006713867</v>
+      </c>
+      <c r="F1391" t="n">
+        <v>260.739990234375</v>
+      </c>
+      <c r="G1391" t="n">
+        <v>260.739990234375</v>
+      </c>
+      <c r="H1391" t="n">
+        <v>2195844</v>
+      </c>
+      <c r="I1391" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/APP.xlsx
+++ b/data/APP.xlsx
@@ -40696,10 +40696,10 @@
         <v>46321.5625</v>
       </c>
       <c r="C1391" t="n">
-        <v>261.100006103516</v>
+        <v>261.385009765625</v>
       </c>
       <c r="D1391" t="n">
-        <v>262.931213378906</v>
+        <v>262.930999755859</v>
       </c>
       <c r="E1391" t="n">
         <v>255.460006713867</v>
@@ -40711,9 +40711,38 @@
         <v>260.739990234375</v>
       </c>
       <c r="H1391" t="n">
-        <v>2195844</v>
+        <v>2197600</v>
       </c>
       <c r="I1391" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1392" s="1" t="n">
+        <v>46322.5625</v>
+      </c>
+      <c r="C1392" t="n">
+        <v>263</v>
+      </c>
+      <c r="D1392" t="n">
+        <v>264.045013427734</v>
+      </c>
+      <c r="E1392" t="n">
+        <v>257.5</v>
+      </c>
+      <c r="F1392" t="n">
+        <v>262.820007324219</v>
+      </c>
+      <c r="G1392" t="n">
+        <v>262.820007324219</v>
+      </c>
+      <c r="H1392" t="n">
+        <v>2259685</v>
+      </c>
+      <c r="I1392" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/APP.xlsx
+++ b/data/APP.xlsx
@@ -40725,7 +40725,7 @@
         <v>46322.5625</v>
       </c>
       <c r="C1392" t="n">
-        <v>263</v>
+        <v>262.5</v>
       </c>
       <c r="D1392" t="n">
         <v>264.045013427734</v>
@@ -40740,9 +40740,38 @@
         <v>262.820007324219</v>
       </c>
       <c r="H1392" t="n">
-        <v>2259685</v>
+        <v>2261400</v>
       </c>
       <c r="I1392" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1393" s="1" t="n">
+        <v>46323.5625</v>
+      </c>
+      <c r="C1393" t="n">
+        <v>257.540008544922</v>
+      </c>
+      <c r="D1393" t="n">
+        <v>262.790008544922</v>
+      </c>
+      <c r="E1393" t="n">
+        <v>257.100006103516</v>
+      </c>
+      <c r="F1393" t="n">
+        <v>259.970001220703</v>
+      </c>
+      <c r="G1393" t="n">
+        <v>259.970001220703</v>
+      </c>
+      <c r="H1393" t="n">
+        <v>2245273</v>
+      </c>
+      <c r="I1393" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/APP.xlsx
+++ b/data/APP.xlsx
@@ -40769,9 +40769,38 @@
         <v>259.970001220703</v>
       </c>
       <c r="H1393" t="n">
-        <v>2245273</v>
+        <v>2257500</v>
       </c>
       <c r="I1393" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1394">
+      <c r="A1394" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1394" s="1" t="n">
+        <v>46324.5625</v>
+      </c>
+      <c r="C1394" t="n">
+        <v>257.760009765625</v>
+      </c>
+      <c r="D1394" t="n">
+        <v>261.179992675781</v>
+      </c>
+      <c r="E1394" t="n">
+        <v>252.009994506836</v>
+      </c>
+      <c r="F1394" t="n">
+        <v>254.910003662109</v>
+      </c>
+      <c r="G1394" t="n">
+        <v>254.910003662109</v>
+      </c>
+      <c r="H1394" t="n">
+        <v>3887425</v>
+      </c>
+      <c r="I1394" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/APP.xlsx
+++ b/data/APP.xlsx
@@ -40783,13 +40783,13 @@
         <v>46324.5625</v>
       </c>
       <c r="C1394" t="n">
-        <v>257.760009765625</v>
+        <v>258.100006103516</v>
       </c>
       <c r="D1394" t="n">
         <v>261.179992675781</v>
       </c>
       <c r="E1394" t="n">
-        <v>252.009994506836</v>
+        <v>252</v>
       </c>
       <c r="F1394" t="n">
         <v>254.910003662109</v>
@@ -40798,9 +40798,38 @@
         <v>254.910003662109</v>
       </c>
       <c r="H1394" t="n">
-        <v>3887425</v>
+        <v>3914500</v>
       </c>
       <c r="I1394" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1395">
+      <c r="A1395" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1395" s="1" t="n">
+        <v>46325.5625</v>
+      </c>
+      <c r="C1395" t="n">
+        <v>242.080001831055</v>
+      </c>
+      <c r="D1395" t="n">
+        <v>242.450698852539</v>
+      </c>
+      <c r="E1395" t="n">
+        <v>225.190093994141</v>
+      </c>
+      <c r="F1395" t="n">
+        <v>228.5</v>
+      </c>
+      <c r="G1395" t="n">
+        <v>228.5</v>
+      </c>
+      <c r="H1395" t="n">
+        <v>9119795</v>
+      </c>
+      <c r="I1395" t="s">
         <v>9</v>
       </c>
     </row>
